--- a/Microsoft_Excel/Build Three Star Financial Model/111.+Exercise+-+before.xlsx
+++ b/Microsoft_Excel/Build Three Star Financial Model/111.+Exercise+-+before.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Financial-Analysis\Microsoft_Excel\Build Three Star Financial Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDC0C60-8AEB-4575-89BF-371771DFBDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3431D64-F3BE-42EC-8654-361A562316C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="675" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Original Source" sheetId="7" r:id="rId1"/>
@@ -21,6 +21,10 @@
     <sheet name="Workings" sheetId="11" r:id="rId6"/>
     <sheet name="P&amp;L" sheetId="15" r:id="rId7"/>
     <sheet name="BS" sheetId="19" r:id="rId8"/>
+    <sheet name="Fixed Asset Roll Forward" sheetId="20" r:id="rId9"/>
+    <sheet name="Financial Liability" sheetId="21" r:id="rId10"/>
+    <sheet name="Equity Schedule" sheetId="22" r:id="rId11"/>
+    <sheet name="Cash Flow" sheetId="23" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Original Source'!#REF!</definedName>
@@ -63,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="177">
   <si>
     <t>Financials</t>
   </si>
@@ -427,9 +431,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Check</t>
   </si>
   <si>
@@ -462,20 +463,159 @@
   <si>
     <t>Selected case</t>
   </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>DSO</t>
+  </si>
+  <si>
+    <t>DPO</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t>Other assets %</t>
+  </si>
+  <si>
+    <t>Other liability %</t>
+  </si>
+  <si>
+    <t>Fixed Asset Roll Forward</t>
+  </si>
+  <si>
+    <t>Beginning PP&amp;E</t>
+  </si>
+  <si>
+    <t>Capex</t>
+  </si>
+  <si>
+    <t>Ending PP&amp;E</t>
+  </si>
+  <si>
+    <t>D&amp;A as a % of beginning PP&amp;E</t>
+  </si>
+  <si>
+    <t>Capex as a % of beginning PP%E</t>
+  </si>
+  <si>
+    <t>Financial Liability</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>Beginning Debt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Debt </t>
+  </si>
+  <si>
+    <t>Principal Repayments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending Debt </t>
+  </si>
+  <si>
+    <t>Debt to be repaid in (years)</t>
+  </si>
+  <si>
+    <t>Annual payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest rate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment </t>
+  </si>
+  <si>
+    <t>Interest expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt repayment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual debt </t>
+  </si>
+  <si>
+    <t>Taxex</t>
+  </si>
+  <si>
+    <t>Equity Schedule</t>
+  </si>
+  <si>
+    <t>Beginning equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incerease of capital </t>
+  </si>
+  <si>
+    <t>Net income(loss)</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>Ending equity</t>
+  </si>
+  <si>
+    <t>Dividends as a % of Net Income</t>
+  </si>
+  <si>
+    <t>Cash Flow</t>
+  </si>
+  <si>
+    <t>Change in Trade receivables</t>
+  </si>
+  <si>
+    <t>Change in Inventory</t>
+  </si>
+  <si>
+    <t>Change in Trade payables</t>
+  </si>
+  <si>
+    <t>Change in Other assets</t>
+  </si>
+  <si>
+    <t>Change in Other liabilities</t>
+  </si>
+  <si>
+    <t>Operating Cash Flow</t>
+  </si>
+  <si>
+    <t>Change in Financial liabilities</t>
+  </si>
+  <si>
+    <t>Change in Equity</t>
+  </si>
+  <si>
+    <t>Change in Provisions</t>
+  </si>
+  <si>
+    <t>Net Cash Flow</t>
+  </si>
+  <si>
+    <t>$ in min</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,8 +734,21 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF002060"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -643,8 +796,13 @@
         <bgColor theme="0" tint="-0.14996795556505021"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="lightGray">
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -696,6 +854,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -708,7 +875,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -771,9 +938,6 @@
     <xf numFmtId="168" fontId="12" fillId="2" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="8" fillId="2" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -785,6 +949,29 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="14" fillId="6" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="4"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="3"/>
+    <xf numFmtId="167" fontId="12" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="2" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -5927,6 +6114,1164 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACAD90E-A859-4550-BA3B-A8027671C796}">
+  <dimension ref="B1:L19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.6328125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.08984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B1" s="23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="F3" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="2:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="25">
+        <v>42004</v>
+      </c>
+      <c r="D4" s="25">
+        <v>42369</v>
+      </c>
+      <c r="E4" s="25">
+        <v>42735</v>
+      </c>
+      <c r="F4" s="25">
+        <v>43100</v>
+      </c>
+      <c r="G4" s="25">
+        <v>43465</v>
+      </c>
+      <c r="H4" s="25">
+        <v>43830</v>
+      </c>
+      <c r="I4" s="25">
+        <v>44196</v>
+      </c>
+      <c r="J4" s="25">
+        <v>44561</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="64">
+        <f>C8</f>
+        <v>615.79999999999995</v>
+      </c>
+      <c r="E5" s="64">
+        <f t="shared" ref="E5:J5" si="0">D8</f>
+        <v>610.4</v>
+      </c>
+      <c r="F5" s="64">
+        <f t="shared" si="0"/>
+        <v>605</v>
+      </c>
+      <c r="G5" s="64">
+        <f t="shared" si="0"/>
+        <v>565.17884560503455</v>
+      </c>
+      <c r="H5" s="64">
+        <f t="shared" si="0"/>
+        <v>521.77378731452222</v>
+      </c>
+      <c r="I5" s="64">
+        <f t="shared" si="0"/>
+        <v>474.4622737778638</v>
+      </c>
+      <c r="J5" s="64">
+        <f t="shared" si="0"/>
+        <v>422.89272402290612</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="64">
+        <v>0</v>
+      </c>
+      <c r="E6" s="64">
+        <v>0</v>
+      </c>
+      <c r="F6" s="64">
+        <v>0</v>
+      </c>
+      <c r="G6" s="64">
+        <v>0</v>
+      </c>
+      <c r="H6" s="64">
+        <v>0</v>
+      </c>
+      <c r="I6" s="64">
+        <v>0</v>
+      </c>
+      <c r="J6" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="64">
+        <f>D8-D5</f>
+        <v>-5.3999999999999773</v>
+      </c>
+      <c r="E7" s="64">
+        <f>E8-E5</f>
+        <v>-5.3999999999999773</v>
+      </c>
+      <c r="F7" s="64">
+        <f>C18</f>
+        <v>-39.82115439496544</v>
+      </c>
+      <c r="G7" s="64">
+        <f t="shared" ref="G7:J7" si="1">D18</f>
+        <v>-43.405058290512329</v>
+      </c>
+      <c r="H7" s="64">
+        <f t="shared" si="1"/>
+        <v>-47.311513536658438</v>
+      </c>
+      <c r="I7" s="64">
+        <f t="shared" si="1"/>
+        <v>-51.569549754957698</v>
+      </c>
+      <c r="J7" s="64">
+        <f t="shared" si="1"/>
+        <v>-56.210809232903884</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="26">
+        <f>BS!C14</f>
+        <v>615.79999999999995</v>
+      </c>
+      <c r="D8" s="26">
+        <f>BS!D14</f>
+        <v>610.4</v>
+      </c>
+      <c r="E8" s="26">
+        <f>BS!E14</f>
+        <v>605</v>
+      </c>
+      <c r="F8" s="26">
+        <f>SUM(F5:F7)</f>
+        <v>565.17884560503455</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" ref="G8:J8" si="2">SUM(G5:G7)</f>
+        <v>521.77378731452222</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="2"/>
+        <v>474.4622737778638</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="2"/>
+        <v>422.89272402290612</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="2"/>
+        <v>366.68191479000222</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="66">
+        <v>10</v>
+      </c>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="66"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="67">
+        <v>0.09</v>
+      </c>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="66"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="64">
+        <f>PMT(C11,C10,E8)</f>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="69">
+        <v>1</v>
+      </c>
+      <c r="D15" s="69">
+        <v>2</v>
+      </c>
+      <c r="E15" s="69">
+        <v>3</v>
+      </c>
+      <c r="F15" s="69">
+        <v>4</v>
+      </c>
+      <c r="G15" s="69">
+        <v>5</v>
+      </c>
+      <c r="H15" s="69">
+        <v>6</v>
+      </c>
+      <c r="I15" s="69">
+        <v>7</v>
+      </c>
+      <c r="J15" s="69">
+        <v>8</v>
+      </c>
+      <c r="K15" s="69">
+        <v>9</v>
+      </c>
+      <c r="L15" s="69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="64">
+        <f>$C$12</f>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="D16" s="64">
+        <f t="shared" ref="D16:L16" si="3">$C$12</f>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="E16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="F16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="G16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="H16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="I16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="J16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="K16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+      <c r="L16" s="64">
+        <f t="shared" si="3"/>
+        <v>-94.271154394965436</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="64">
+        <f>-E8*C11</f>
+        <v>-54.449999999999996</v>
+      </c>
+      <c r="D17" s="64">
+        <f>-C19*$C$11</f>
+        <v>-50.866096104453106</v>
+      </c>
+      <c r="E17" s="64">
+        <f>-D19*$C$11</f>
+        <v>-46.959640858306997</v>
+      </c>
+      <c r="F17" s="64">
+        <f t="shared" ref="E17:L17" si="4">-E19*$C$11</f>
+        <v>-42.701604640007737</v>
+      </c>
+      <c r="G17" s="64">
+        <f t="shared" si="4"/>
+        <v>-38.060345162061552</v>
+      </c>
+      <c r="H17" s="64">
+        <f t="shared" si="4"/>
+        <v>-33.0013723311002</v>
+      </c>
+      <c r="I17" s="64">
+        <f t="shared" si="4"/>
+        <v>-27.487091945352326</v>
+      </c>
+      <c r="J17" s="64">
+        <f t="shared" si="4"/>
+        <v>-21.476526324887146</v>
+      </c>
+      <c r="K17" s="64">
+        <f t="shared" si="4"/>
+        <v>-14.925009798580101</v>
+      </c>
+      <c r="L17" s="64">
+        <f t="shared" si="4"/>
+        <v>-7.7838567849054208</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="64">
+        <f>C16-C17</f>
+        <v>-39.82115439496544</v>
+      </c>
+      <c r="D18" s="64">
+        <f t="shared" ref="D18:L18" si="5">D16-D17</f>
+        <v>-43.405058290512329</v>
+      </c>
+      <c r="E18" s="64">
+        <f t="shared" si="5"/>
+        <v>-47.311513536658438</v>
+      </c>
+      <c r="F18" s="64">
+        <f t="shared" si="5"/>
+        <v>-51.569549754957698</v>
+      </c>
+      <c r="G18" s="64">
+        <f t="shared" si="5"/>
+        <v>-56.210809232903884</v>
+      </c>
+      <c r="H18" s="64">
+        <f t="shared" si="5"/>
+        <v>-61.269782063865236</v>
+      </c>
+      <c r="I18" s="64">
+        <f t="shared" si="5"/>
+        <v>-66.784062449613117</v>
+      </c>
+      <c r="J18" s="64">
+        <f t="shared" si="5"/>
+        <v>-72.794628070078289</v>
+      </c>
+      <c r="K18" s="64">
+        <f t="shared" si="5"/>
+        <v>-79.346144596385329</v>
+      </c>
+      <c r="L18" s="64">
+        <f t="shared" si="5"/>
+        <v>-86.487297610060011</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="64">
+        <f>E8+C18</f>
+        <v>565.17884560503455</v>
+      </c>
+      <c r="D19" s="64">
+        <f>C19+D18</f>
+        <v>521.77378731452222</v>
+      </c>
+      <c r="E19" s="64">
+        <f t="shared" ref="E19:L19" si="6">D19+E18</f>
+        <v>474.4622737778638</v>
+      </c>
+      <c r="F19" s="64">
+        <f t="shared" si="6"/>
+        <v>422.89272402290612</v>
+      </c>
+      <c r="G19" s="64">
+        <f t="shared" si="6"/>
+        <v>366.68191479000222</v>
+      </c>
+      <c r="H19" s="64">
+        <f t="shared" si="6"/>
+        <v>305.41213272613697</v>
+      </c>
+      <c r="I19" s="64">
+        <f t="shared" si="6"/>
+        <v>238.62807027652386</v>
+      </c>
+      <c r="J19" s="64">
+        <f t="shared" si="6"/>
+        <v>165.83344220644557</v>
+      </c>
+      <c r="K19" s="64">
+        <f t="shared" si="6"/>
+        <v>86.487297610060239</v>
+      </c>
+      <c r="L19" s="64">
+        <f t="shared" si="6"/>
+        <v>2.2737367544323206E-13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B7BC8BA-3BF4-4D0B-9922-935ED8B6A670}">
+  <dimension ref="B1:J12"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.6328125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="10.08984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F3" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="25">
+        <v>42004</v>
+      </c>
+      <c r="D4" s="25">
+        <v>42369</v>
+      </c>
+      <c r="E4" s="25">
+        <v>42735</v>
+      </c>
+      <c r="F4" s="25">
+        <v>43100</v>
+      </c>
+      <c r="G4" s="25">
+        <v>43465</v>
+      </c>
+      <c r="H4" s="25">
+        <v>43830</v>
+      </c>
+      <c r="I4" s="25">
+        <v>44196</v>
+      </c>
+      <c r="J4" s="25">
+        <v>44561</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="64">
+        <f>E9</f>
+        <v>485.3</v>
+      </c>
+      <c r="G5" s="64">
+        <f t="shared" ref="G5:J5" ca="1" si="0">F9</f>
+        <v>691.01555059288535</v>
+      </c>
+      <c r="H5" s="64">
+        <f t="shared" ca="1" si="0"/>
+        <v>905.08695515642376</v>
+      </c>
+      <c r="I5" s="64">
+        <f t="shared" ca="1" si="0"/>
+        <v>1127.8519457029515</v>
+      </c>
+      <c r="J5" s="64">
+        <f ca="1">I9</f>
+        <v>1359.6660020586651</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="64">
+        <v>0</v>
+      </c>
+      <c r="G6" s="64">
+        <v>0</v>
+      </c>
+      <c r="H6" s="64">
+        <v>0</v>
+      </c>
+      <c r="I6" s="64">
+        <v>0</v>
+      </c>
+      <c r="J6" s="64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="64">
+        <f ca="1">'P&amp;L'!I16</f>
+        <v>342.85925098814226</v>
+      </c>
+      <c r="G7" s="64">
+        <f ca="1">'P&amp;L'!J16</f>
+        <v>356.78567427256388</v>
+      </c>
+      <c r="H7" s="64">
+        <f ca="1">'P&amp;L'!K16</f>
+        <v>371.27498424421293</v>
+      </c>
+      <c r="I7" s="64">
+        <f ca="1">'P&amp;L'!L16</f>
+        <v>386.35676059285606</v>
+      </c>
+      <c r="J7" s="64">
+        <f ca="1">'P&amp;L'!M16</f>
+        <v>402.06260497856908</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="64">
+        <f ca="1">IF(F7&gt;0,-F11*F7,0)</f>
+        <v>-137.1437003952569</v>
+      </c>
+      <c r="G8" s="64">
+        <f t="shared" ref="G8:J8" ca="1" si="1">IF(G7&gt;0,-G11*G7,0)</f>
+        <v>-142.71426970902556</v>
+      </c>
+      <c r="H8" s="64">
+        <f t="shared" ca="1" si="1"/>
+        <v>-148.50999369768519</v>
+      </c>
+      <c r="I8" s="64">
+        <f t="shared" ca="1" si="1"/>
+        <v>-154.54270423714243</v>
+      </c>
+      <c r="J8" s="64">
+        <f t="shared" ca="1" si="1"/>
+        <v>-160.82504199142764</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26">
+        <f>BS!E16</f>
+        <v>485.3</v>
+      </c>
+      <c r="F9" s="26">
+        <f ca="1">SUM(F5:F8)</f>
+        <v>691.01555059288535</v>
+      </c>
+      <c r="G9" s="26">
+        <f t="shared" ref="G9:J9" ca="1" si="2">SUM(G5:G8)</f>
+        <v>905.08695515642376</v>
+      </c>
+      <c r="H9" s="26">
+        <f t="shared" ca="1" si="2"/>
+        <v>1127.8519457029515</v>
+      </c>
+      <c r="I9" s="26">
+        <f t="shared" ca="1" si="2"/>
+        <v>1359.6660020586651</v>
+      </c>
+      <c r="J9" s="26">
+        <f t="shared" ca="1" si="2"/>
+        <v>1600.9035650458065</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="60">
+        <v>0.4</v>
+      </c>
+      <c r="H11" s="60">
+        <v>0.4</v>
+      </c>
+      <c r="I11" s="60">
+        <v>0.4</v>
+      </c>
+      <c r="J11" s="60">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9745C34-1B14-46A0-8AF8-E11F87B2CAF7}">
+  <dimension ref="B1:J19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.26953125" style="22" customWidth="1"/>
+    <col min="2" max="5" width="8.7265625" style="22"/>
+    <col min="6" max="6" width="9.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="70" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="70"/>
+    </row>
+    <row r="3" spans="2:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="70"/>
+      <c r="F3" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+    </row>
+    <row r="4" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30">
+        <v>2017</v>
+      </c>
+      <c r="G4" s="30">
+        <v>2018</v>
+      </c>
+      <c r="H4" s="30">
+        <v>2019</v>
+      </c>
+      <c r="I4" s="30">
+        <v>2020</v>
+      </c>
+      <c r="J4" s="30">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="64">
+        <f ca="1">'P&amp;L'!I10</f>
+        <v>626.24</v>
+      </c>
+      <c r="G5" s="64">
+        <f ca="1">'P&amp;L'!J10</f>
+        <v>645.02719999999999</v>
+      </c>
+      <c r="H5" s="64">
+        <f ca="1">'P&amp;L'!K10</f>
+        <v>664.37801600000012</v>
+      </c>
+      <c r="I5" s="64">
+        <f ca="1">'P&amp;L'!L10</f>
+        <v>684.30935648000013</v>
+      </c>
+      <c r="J5" s="64">
+        <f ca="1">'P&amp;L'!M10</f>
+        <v>704.83863717440022</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="64">
+        <f>'P&amp;L'!I13</f>
+        <v>-54.449999999999996</v>
+      </c>
+      <c r="G6" s="64">
+        <f>'P&amp;L'!J13</f>
+        <v>-50.866096104453106</v>
+      </c>
+      <c r="H6" s="64">
+        <f>'P&amp;L'!K13</f>
+        <v>-46.959640858306997</v>
+      </c>
+      <c r="I6" s="64">
+        <f>'P&amp;L'!L13</f>
+        <v>-42.701604640007737</v>
+      </c>
+      <c r="J6" s="64">
+        <f>'P&amp;L'!M13</f>
+        <v>-38.060345162061552</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="64">
+        <f ca="1">'P&amp;L'!I15</f>
+        <v>-184.61651976284583</v>
+      </c>
+      <c r="G7" s="64">
+        <f ca="1">'P&amp;L'!J15</f>
+        <v>-192.11536306984209</v>
+      </c>
+      <c r="H7" s="64">
+        <f ca="1">'P&amp;L'!K15</f>
+        <v>-199.91729920842232</v>
+      </c>
+      <c r="I7" s="64">
+        <f ca="1">'P&amp;L'!L15</f>
+        <v>-208.03825570384558</v>
+      </c>
+      <c r="J7" s="64">
+        <f ca="1">'P&amp;L'!M15</f>
+        <v>-216.4952488346141</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="64">
+        <f ca="1">-(BS!F5-BS!E5)</f>
+        <v>5.627420635663384</v>
+      </c>
+      <c r="G8" s="64">
+        <f ca="1">-(BS!G5-BS!F5)</f>
+        <v>-4.9101773809300937</v>
+      </c>
+      <c r="H8" s="64">
+        <f ca="1">-(BS!H5-BS!G5)</f>
+        <v>-5.0574827023580156</v>
+      </c>
+      <c r="I8" s="64">
+        <f ca="1">-(BS!I5-BS!H5)</f>
+        <v>-5.2092071834287594</v>
+      </c>
+      <c r="J8" s="64">
+        <f ca="1">-(BS!J5-BS!I5)</f>
+        <v>-5.3654833989315875</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" s="64">
+        <f ca="1">-(BS!F6-BS!E6)</f>
+        <v>12.465696356761697</v>
+      </c>
+      <c r="G9" s="64">
+        <f ca="1">-(BS!G6-BS!F6)</f>
+        <v>-2.9260291092971755</v>
+      </c>
+      <c r="H9" s="64">
+        <f ca="1">-(BS!H6-BS!G6)</f>
+        <v>-3.0138099825760776</v>
+      </c>
+      <c r="I9" s="64">
+        <f ca="1">-(BS!I6-BS!H6)</f>
+        <v>-3.1042242820533232</v>
+      </c>
+      <c r="J9" s="64">
+        <f ca="1">-(BS!J6-BS!I6)</f>
+        <v>-3.1973510105149501</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="64">
+        <f ca="1">BS!F12-BS!E12</f>
+        <v>0.96881426626879374</v>
+      </c>
+      <c r="G10" s="64">
+        <f ca="1">BS!G12-BS!F12</f>
+        <v>2.0960644279880682</v>
+      </c>
+      <c r="H10" s="64">
+        <f ca="1">BS!H12-BS!G12</f>
+        <v>2.1589463608276986</v>
+      </c>
+      <c r="I10" s="64">
+        <f ca="1">BS!I12-BS!H12</f>
+        <v>2.2237147516525368</v>
+      </c>
+      <c r="J10" s="64">
+        <f ca="1">BS!J12-BS!I12</f>
+        <v>2.2904261942021265</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="64">
+        <f ca="1">-(BS!F9-BS!E9)</f>
+        <v>11.853411028107011</v>
+      </c>
+      <c r="G11" s="64">
+        <f ca="1">-(BS!G9-BS!F9)</f>
+        <v>-1.6843976691567946</v>
+      </c>
+      <c r="H11" s="64">
+        <f ca="1">-(BS!H9-BS!G9)</f>
+        <v>-1.7349295992314993</v>
+      </c>
+      <c r="I11" s="64">
+        <f ca="1">-(BS!I9-BS!H9)</f>
+        <v>-1.7869774872084392</v>
+      </c>
+      <c r="J11" s="64">
+        <f ca="1">-(BS!J9-BS!I9)</f>
+        <v>-1.8405868118246929</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" s="64">
+        <f ca="1">BS!F15-BS!E15</f>
+        <v>6.8536690999040317</v>
+      </c>
+      <c r="G12" s="64">
+        <f ca="1">BS!G15-BS!F15</f>
+        <v>1.3726100729971193</v>
+      </c>
+      <c r="H12" s="64">
+        <f ca="1">BS!H15-BS!G15</f>
+        <v>1.413788375187039</v>
+      </c>
+      <c r="I12" s="64">
+        <f ca="1">BS!I15-BS!H15</f>
+        <v>1.4562020264426465</v>
+      </c>
+      <c r="J12" s="64">
+        <f ca="1">BS!J15-BS!I15</f>
+        <v>1.4998880872359308</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="64">
+        <f>-'Fixed Asset Roll Forward'!F7</f>
+        <v>-58.390513833992095</v>
+      </c>
+      <c r="G13" s="64">
+        <f>-'Fixed Asset Roll Forward'!G7</f>
+        <v>-59.63679357590339</v>
+      </c>
+      <c r="H13" s="64">
+        <f>-'Fixed Asset Roll Forward'!H7</f>
+        <v>-60.909673754993825</v>
+      </c>
+      <c r="I13" s="64">
+        <f>-'Fixed Asset Roll Forward'!I7</f>
+        <v>-62.209722127630052</v>
+      </c>
+      <c r="J13" s="64">
+        <f>-'Fixed Asset Roll Forward'!J7</f>
+        <v>-63.537518568298829</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="71" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72">
+        <f ca="1">SUM(F5:F13)</f>
+        <v>366.55197778986701</v>
+      </c>
+      <c r="G14" s="72">
+        <f t="shared" ref="G14:J14" ca="1" si="0">SUM(G5:G13)</f>
+        <v>336.35701759140255</v>
+      </c>
+      <c r="H14" s="72">
+        <f t="shared" ca="1" si="0"/>
+        <v>350.35791463012606</v>
+      </c>
+      <c r="I14" s="72">
+        <f t="shared" ca="1" si="0"/>
+        <v>364.93928183392137</v>
+      </c>
+      <c r="J14" s="72">
+        <f t="shared" ca="1" si="0"/>
+        <v>380.1324176695926</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="64">
+        <f ca="1">'Equity Schedule'!F8</f>
+        <v>-137.1437003952569</v>
+      </c>
+      <c r="G15" s="64">
+        <f ca="1">'Equity Schedule'!G8</f>
+        <v>-142.71426970902556</v>
+      </c>
+      <c r="H15" s="64">
+        <f ca="1">'Equity Schedule'!H8</f>
+        <v>-148.50999369768519</v>
+      </c>
+      <c r="I15" s="64">
+        <f ca="1">'Equity Schedule'!I8</f>
+        <v>-154.54270423714243</v>
+      </c>
+      <c r="J15" s="64">
+        <f ca="1">'Equity Schedule'!J8</f>
+        <v>-160.82504199142764</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" s="64">
+        <f>'Financial Liability'!F8-'Financial Liability'!E8</f>
+        <v>-39.821154394965447</v>
+      </c>
+      <c r="G16" s="64">
+        <f>'Financial Liability'!G8-'Financial Liability'!F8</f>
+        <v>-43.405058290512329</v>
+      </c>
+      <c r="H16" s="64">
+        <f>'Financial Liability'!H8-'Financial Liability'!G8</f>
+        <v>-47.311513536658424</v>
+      </c>
+      <c r="I16" s="64">
+        <f>'Financial Liability'!I8-'Financial Liability'!H8</f>
+        <v>-51.569549754957677</v>
+      </c>
+      <c r="J16" s="64">
+        <f>'Financial Liability'!J8-'Financial Liability'!I8</f>
+        <v>-56.210809232903898</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="64">
+        <f>BS!F13-BS!E13</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="64">
+        <f>BS!G13-BS!F13</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="64">
+        <f>BS!H13-BS!G13</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="64">
+        <f>BS!I13-BS!H13</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="64">
+        <f>BS!J13-BS!I13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="64">
+        <f ca="1">'Equity Schedule'!F9-'Equity Schedule'!E9-'Equity Schedule'!F7-'Equity Schedule'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="64">
+        <f ca="1">'Equity Schedule'!G9-'Equity Schedule'!F9-'Equity Schedule'!G7-'Equity Schedule'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="64">
+        <f ca="1">'Equity Schedule'!H9-'Equity Schedule'!G9-'Equity Schedule'!H7-'Equity Schedule'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="64">
+        <f ca="1">'Equity Schedule'!I9-'Equity Schedule'!H9-'Equity Schedule'!I7-'Equity Schedule'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="64">
+        <f ca="1">'Equity Schedule'!J9-'Equity Schedule'!I9-'Equity Schedule'!J7-'Equity Schedule'!J8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="73">
+        <f ca="1">SUM(F14:F18)</f>
+        <v>189.58712299964466</v>
+      </c>
+      <c r="G19" s="73">
+        <f t="shared" ref="G19:J19" ca="1" si="1">SUM(G14:G18)</f>
+        <v>150.23768959186467</v>
+      </c>
+      <c r="H19" s="73">
+        <f t="shared" ca="1" si="1"/>
+        <v>154.53640739578245</v>
+      </c>
+      <c r="I19" s="73">
+        <f t="shared" ca="1" si="1"/>
+        <v>158.82702784182126</v>
+      </c>
+      <c r="J19" s="73">
+        <f t="shared" ca="1" si="1"/>
+        <v>163.09656644526106</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C55"/>
@@ -15334,23 +16679,23 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E4" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="I4" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
     </row>
     <row r="5" spans="2:13" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="29" t="s">
@@ -15636,11 +16981,26 @@
         <f t="shared" si="0"/>
         <v>-6.8181818181818232E-2</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
+      <c r="I11" s="32">
+        <f>'Fixed Asset Roll Forward'!F6</f>
+        <v>-44.314229249011859</v>
+      </c>
+      <c r="J11" s="32">
+        <f>'Fixed Asset Roll Forward'!G6</f>
+        <v>-45.260066553140966</v>
+      </c>
+      <c r="K11" s="32">
+        <f>'Fixed Asset Roll Forward'!H6</f>
+        <v>-46.22609168905781</v>
+      </c>
+      <c r="L11" s="32">
+        <f>'Fixed Asset Roll Forward'!I6</f>
+        <v>-47.212735543290663</v>
+      </c>
+      <c r="M11" s="32">
+        <f>'Fixed Asset Roll Forward'!J6</f>
+        <v>-48.22043819915536</v>
+      </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="34" t="s">
@@ -15668,23 +17028,23 @@
       </c>
       <c r="I12" s="34">
         <f ca="1">SUM(I10:I11)</f>
-        <v>626.24</v>
+        <v>581.92577075098814</v>
       </c>
       <c r="J12" s="34">
         <f t="shared" ref="J12:M12" ca="1" si="7">SUM(J10:J11)</f>
-        <v>645.02719999999999</v>
+        <v>599.76713344685902</v>
       </c>
       <c r="K12" s="34">
         <f t="shared" ca="1" si="7"/>
-        <v>664.37801600000012</v>
+        <v>618.15192431094226</v>
       </c>
       <c r="L12" s="34">
         <f t="shared" ca="1" si="7"/>
-        <v>684.30935648000013</v>
+        <v>637.09662093670943</v>
       </c>
       <c r="M12" s="34">
         <f t="shared" ca="1" si="7"/>
-        <v>704.83863717440022</v>
+        <v>656.61819897524481</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.3">
@@ -15711,11 +17071,26 @@
         <f t="shared" si="0"/>
         <v>-0.19999999999999996</v>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
+      <c r="I13" s="32">
+        <f>'Financial Liability'!C17</f>
+        <v>-54.449999999999996</v>
+      </c>
+      <c r="J13" s="32">
+        <f>'Financial Liability'!D17</f>
+        <v>-50.866096104453106</v>
+      </c>
+      <c r="K13" s="32">
+        <f>'Financial Liability'!E17</f>
+        <v>-46.959640858306997</v>
+      </c>
+      <c r="L13" s="32">
+        <f>'Financial Liability'!F17</f>
+        <v>-42.701604640007737</v>
+      </c>
+      <c r="M13" s="32">
+        <f>'Financial Liability'!G17</f>
+        <v>-38.060345162061552</v>
+      </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="34" t="s">
@@ -15743,23 +17118,23 @@
       </c>
       <c r="I14" s="34">
         <f ca="1">SUM(I12:I13)</f>
-        <v>626.24</v>
+        <v>527.47577075098809</v>
       </c>
       <c r="J14" s="34">
         <f t="shared" ref="J14:M14" ca="1" si="8">SUM(J12:J13)</f>
-        <v>645.02719999999999</v>
+        <v>548.90103734240597</v>
       </c>
       <c r="K14" s="34">
         <f t="shared" ca="1" si="8"/>
-        <v>664.37801600000012</v>
+        <v>571.19228345263525</v>
       </c>
       <c r="L14" s="34">
         <f t="shared" ca="1" si="8"/>
-        <v>684.30935648000013</v>
+        <v>594.39501629670167</v>
       </c>
       <c r="M14" s="34">
         <f t="shared" ca="1" si="8"/>
-        <v>704.83863717440022</v>
+        <v>618.55785381318321</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.3">
@@ -15786,11 +17161,26 @@
         <f t="shared" si="0"/>
         <v>-6.6673016477759584E-3</v>
       </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
+      <c r="I15" s="32">
+        <f ca="1">I14*I37</f>
+        <v>-184.61651976284583</v>
+      </c>
+      <c r="J15" s="32">
+        <f t="shared" ref="J15:M15" ca="1" si="9">J14*J37</f>
+        <v>-192.11536306984209</v>
+      </c>
+      <c r="K15" s="32">
+        <f t="shared" ca="1" si="9"/>
+        <v>-199.91729920842232</v>
+      </c>
+      <c r="L15" s="32">
+        <f t="shared" ca="1" si="9"/>
+        <v>-208.03825570384558</v>
+      </c>
+      <c r="M15" s="32">
+        <f t="shared" ca="1" si="9"/>
+        <v>-216.4952488346141</v>
+      </c>
     </row>
     <row r="16" spans="2:13" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="36" t="s">
@@ -15818,508 +17208,540 @@
       </c>
       <c r="I16" s="36">
         <f ca="1">SUM(I14:I15)</f>
-        <v>626.24</v>
+        <v>342.85925098814226</v>
       </c>
       <c r="J16" s="36">
-        <f t="shared" ref="J16:M16" ca="1" si="9">SUM(J14:J15)</f>
-        <v>645.02719999999999</v>
+        <f t="shared" ref="J16:M16" ca="1" si="10">SUM(J14:J15)</f>
+        <v>356.78567427256388</v>
       </c>
       <c r="K16" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>664.37801600000012</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>371.27498424421293</v>
       </c>
       <c r="L16" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>684.30935648000013</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>386.35676059285606</v>
       </c>
       <c r="M16" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>704.83863717440022</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>402.06260497856908</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+    </row>
+    <row r="19" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-    </row>
-    <row r="19" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="45"/>
-      <c r="M19" s="45"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
     </row>
     <row r="20" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B20" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="51">
+      <c r="B20" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="50">
         <f ca="1">OFFSET(I20,MATCH($C$3,$B21:$B23,0),0)</f>
         <v>0.03</v>
       </c>
-      <c r="J20" s="51">
-        <f t="shared" ref="J20:M20" ca="1" si="10">OFFSET(J20,MATCH($C$3,$B21:$B23,0),0)</f>
+      <c r="J20" s="50">
+        <f t="shared" ref="J20:M20" ca="1" si="11">OFFSET(J20,MATCH($C$3,$B21:$B23,0),0)</f>
         <v>0.03</v>
       </c>
-      <c r="K20" s="51">
-        <f t="shared" ca="1" si="10"/>
+      <c r="K20" s="50">
+        <f t="shared" ca="1" si="11"/>
         <v>0.03</v>
       </c>
-      <c r="L20" s="51">
-        <f t="shared" ca="1" si="10"/>
+      <c r="L20" s="50">
+        <f t="shared" ca="1" si="11"/>
         <v>0.03</v>
       </c>
-      <c r="M20" s="51">
-        <f t="shared" ca="1" si="10"/>
+      <c r="M20" s="50">
+        <f t="shared" ca="1" si="11"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="J21" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="K21" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="L21" s="51">
+        <v>0.03</v>
+      </c>
+      <c r="M21" s="51">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="J21" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="K21" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="L21" s="52">
-        <v>0.03</v>
-      </c>
-      <c r="M21" s="52">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B22" s="45" t="s">
+      <c r="C22" s="48"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="J22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="K22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="L22" s="51">
+        <v>0.02</v>
+      </c>
+      <c r="M22" s="51">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="52">
-        <v>0.02</v>
-      </c>
-      <c r="J22" s="52">
-        <v>0.02</v>
-      </c>
-      <c r="K22" s="52">
-        <v>0.02</v>
-      </c>
-      <c r="L22" s="52">
-        <v>0.02</v>
-      </c>
-      <c r="M22" s="52">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B23" s="46" t="s">
+      <c r="C23" s="48"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="J23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="K23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="L23" s="51">
+        <v>0.01</v>
+      </c>
+      <c r="M23" s="51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B24" s="45"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+    </row>
+    <row r="25" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="52">
-        <v>0.01</v>
-      </c>
-      <c r="J23" s="52">
-        <v>0.01</v>
-      </c>
-      <c r="K23" s="52">
-        <v>0.01</v>
-      </c>
-      <c r="L23" s="52">
-        <v>0.01</v>
-      </c>
-      <c r="M23" s="52">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B24" s="46"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-    </row>
-    <row r="25" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B25" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
     </row>
     <row r="26" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="51">
+      <c r="B26" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="50">
         <f ca="1">OFFSET(I26,MATCH($C$3,$B27:$B29,0),0)</f>
         <v>-0.45</v>
       </c>
-      <c r="J26" s="51">
-        <f t="shared" ref="J26" ca="1" si="11">OFFSET(J26,MATCH($C$3,$B27:$B29,0),0)</f>
+      <c r="J26" s="50">
+        <f t="shared" ref="J26" ca="1" si="12">OFFSET(J26,MATCH($C$3,$B27:$B29,0),0)</f>
         <v>-0.45</v>
       </c>
-      <c r="K26" s="51">
-        <f t="shared" ref="K26" ca="1" si="12">OFFSET(K26,MATCH($C$3,$B27:$B29,0),0)</f>
+      <c r="K26" s="50">
+        <f t="shared" ref="K26" ca="1" si="13">OFFSET(K26,MATCH($C$3,$B27:$B29,0),0)</f>
         <v>-0.45</v>
       </c>
-      <c r="L26" s="51">
-        <f t="shared" ref="L26" ca="1" si="13">OFFSET(L26,MATCH($C$3,$B27:$B29,0),0)</f>
+      <c r="L26" s="50">
+        <f t="shared" ref="L26" ca="1" si="14">OFFSET(L26,MATCH($C$3,$B27:$B29,0),0)</f>
         <v>-0.45</v>
       </c>
-      <c r="M26" s="51">
-        <f t="shared" ref="M26" ca="1" si="14">OFFSET(M26,MATCH($C$3,$B27:$B29,0),0)</f>
+      <c r="M26" s="50">
+        <f t="shared" ref="M26" ca="1" si="15">OFFSET(M26,MATCH($C$3,$B27:$B29,0),0)</f>
         <v>-0.45</v>
       </c>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B27" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="54">
+      <c r="B27" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="53">
         <f>C$7/C$6</f>
         <v>-0.47946611909650921</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="53">
         <f>D$7/D$6</f>
         <v>-0.46347184986595175</v>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="53">
         <f>E$7/E$6</f>
         <v>-0.44967105263157897</v>
       </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="52">
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="51">
         <v>-0.45</v>
       </c>
-      <c r="J27" s="52">
+      <c r="J27" s="51">
         <v>-0.45</v>
       </c>
-      <c r="K27" s="52">
+      <c r="K27" s="51">
         <v>-0.45</v>
       </c>
-      <c r="L27" s="52">
+      <c r="L27" s="51">
         <v>-0.45</v>
       </c>
-      <c r="M27" s="52">
+      <c r="M27" s="51">
         <v>-0.45</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="53">
+        <f t="shared" ref="C28:E29" si="16">C$7/C$6</f>
+        <v>-0.47946611909650921</v>
+      </c>
+      <c r="D28" s="53">
+        <f t="shared" si="16"/>
+        <v>-0.46347184986595175</v>
+      </c>
+      <c r="E28" s="53">
+        <f t="shared" si="16"/>
+        <v>-0.44967105263157897</v>
+      </c>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="51">
+        <v>-0.46</v>
+      </c>
+      <c r="J28" s="51">
+        <v>-0.46</v>
+      </c>
+      <c r="K28" s="51">
+        <v>-0.46</v>
+      </c>
+      <c r="L28" s="51">
+        <v>-0.46</v>
+      </c>
+      <c r="M28" s="51">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B29" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="54">
-        <f t="shared" ref="C28:E29" si="15">C$7/C$6</f>
+      <c r="C29" s="53">
+        <f t="shared" si="16"/>
         <v>-0.47946611909650921</v>
       </c>
-      <c r="D28" s="54">
-        <f t="shared" si="15"/>
+      <c r="D29" s="53">
+        <f t="shared" si="16"/>
         <v>-0.46347184986595175</v>
       </c>
-      <c r="E28" s="54">
-        <f t="shared" si="15"/>
+      <c r="E29" s="53">
+        <f t="shared" si="16"/>
         <v>-0.44967105263157897</v>
       </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="52">
-        <v>-0.46</v>
-      </c>
-      <c r="J28" s="52">
-        <v>-0.46</v>
-      </c>
-      <c r="K28" s="52">
-        <v>-0.46</v>
-      </c>
-      <c r="L28" s="52">
-        <v>-0.46</v>
-      </c>
-      <c r="M28" s="52">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B29" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="54">
-        <f t="shared" si="15"/>
-        <v>-0.47946611909650921</v>
-      </c>
-      <c r="D29" s="54">
-        <f t="shared" si="15"/>
-        <v>-0.46347184986595175</v>
-      </c>
-      <c r="E29" s="54">
-        <f t="shared" si="15"/>
-        <v>-0.44967105263157897</v>
-      </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="52">
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="51">
         <v>-0.47</v>
       </c>
-      <c r="J29" s="52">
+      <c r="J29" s="51">
         <v>-0.47</v>
       </c>
-      <c r="K29" s="52">
+      <c r="K29" s="51">
         <v>-0.47</v>
       </c>
-      <c r="L29" s="52">
+      <c r="L29" s="51">
         <v>-0.47</v>
       </c>
-      <c r="M29" s="52">
+      <c r="M29" s="51">
         <v>-0.47</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B30" s="45"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
     </row>
     <row r="31" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+    </row>
+    <row r="32" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="C31" s="53"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-    </row>
-    <row r="32" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="51">
+      <c r="C32" s="52"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="50">
         <f ca="1">OFFSET(I32,MATCH($C$3,$B33:$B35,0),0)</f>
         <v>-0.35</v>
       </c>
-      <c r="J32" s="51">
-        <f t="shared" ref="J32" ca="1" si="16">OFFSET(J32,MATCH($C$3,$B33:$B35,0),0)</f>
+      <c r="J32" s="50">
+        <f t="shared" ref="J32" ca="1" si="17">OFFSET(J32,MATCH($C$3,$B33:$B35,0),0)</f>
         <v>-0.35</v>
       </c>
-      <c r="K32" s="51">
-        <f t="shared" ref="K32" ca="1" si="17">OFFSET(K32,MATCH($C$3,$B33:$B35,0),0)</f>
+      <c r="K32" s="50">
+        <f t="shared" ref="K32" ca="1" si="18">OFFSET(K32,MATCH($C$3,$B33:$B35,0),0)</f>
         <v>-0.35</v>
       </c>
-      <c r="L32" s="51">
-        <f t="shared" ref="L32" ca="1" si="18">OFFSET(L32,MATCH($C$3,$B33:$B35,0),0)</f>
+      <c r="L32" s="50">
+        <f t="shared" ref="L32" ca="1" si="19">OFFSET(L32,MATCH($C$3,$B33:$B35,0),0)</f>
         <v>-0.35</v>
       </c>
-      <c r="M32" s="51">
-        <f t="shared" ref="M32" ca="1" si="19">OFFSET(M32,MATCH($C$3,$B33:$B35,0),0)</f>
+      <c r="M32" s="50">
+        <f t="shared" ref="M32" ca="1" si="20">OFFSET(M32,MATCH($C$3,$B33:$B35,0),0)</f>
         <v>-0.35</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="54">
+      <c r="B33" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="53">
         <f>C$9/C$6</f>
         <v>-0.41484599589322374</v>
       </c>
-      <c r="D33" s="54">
-        <f t="shared" ref="D33:E35" si="20">D$9/D$6</f>
+      <c r="D33" s="53">
+        <f t="shared" ref="D33:E35" si="21">D$9/D$6</f>
         <v>-0.4173391420911528</v>
       </c>
-      <c r="E33" s="54">
-        <f t="shared" si="20"/>
+      <c r="E33" s="53">
+        <f t="shared" si="21"/>
         <v>-0.35139473684210526</v>
       </c>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="52">
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="51">
         <v>-0.35</v>
       </c>
-      <c r="J33" s="52">
+      <c r="J33" s="51">
         <v>-0.35</v>
       </c>
-      <c r="K33" s="52">
+      <c r="K33" s="51">
         <v>-0.35</v>
       </c>
-      <c r="L33" s="52">
+      <c r="L33" s="51">
         <v>-0.35</v>
       </c>
-      <c r="M33" s="52">
+      <c r="M33" s="51">
         <v>-0.35</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" s="53">
+        <f t="shared" ref="C34:C35" si="22">C$9/C$6</f>
+        <v>-0.41484599589322374</v>
+      </c>
+      <c r="D34" s="53">
+        <f t="shared" si="21"/>
+        <v>-0.4173391420911528</v>
+      </c>
+      <c r="E34" s="53">
+        <f t="shared" si="21"/>
+        <v>-0.35139473684210526</v>
+      </c>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="51">
+        <v>-0.39</v>
+      </c>
+      <c r="J34" s="51">
+        <v>-0.39</v>
+      </c>
+      <c r="K34" s="51">
+        <v>-0.39</v>
+      </c>
+      <c r="L34" s="51">
+        <v>-0.39</v>
+      </c>
+      <c r="M34" s="51">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C34" s="54">
-        <f t="shared" ref="C34:C35" si="21">C$9/C$6</f>
+      <c r="C35" s="53">
+        <f t="shared" si="22"/>
         <v>-0.41484599589322374</v>
       </c>
-      <c r="D34" s="54">
-        <f t="shared" si="20"/>
+      <c r="D35" s="53">
+        <f t="shared" si="21"/>
         <v>-0.4173391420911528</v>
       </c>
-      <c r="E34" s="54">
-        <f t="shared" si="20"/>
+      <c r="E35" s="53">
+        <f t="shared" si="21"/>
         <v>-0.35139473684210526</v>
       </c>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="52">
-        <v>-0.39</v>
-      </c>
-      <c r="J34" s="52">
-        <v>-0.39</v>
-      </c>
-      <c r="K34" s="52">
-        <v>-0.39</v>
-      </c>
-      <c r="L34" s="52">
-        <v>-0.39</v>
-      </c>
-      <c r="M34" s="52">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B35" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" s="54">
-        <f t="shared" si="21"/>
-        <v>-0.41484599589322374</v>
-      </c>
-      <c r="D35" s="54">
-        <f t="shared" si="20"/>
-        <v>-0.4173391420911528</v>
-      </c>
-      <c r="E35" s="54">
-        <f t="shared" si="20"/>
-        <v>-0.35139473684210526</v>
-      </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="52">
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="51">
         <v>-0.41</v>
       </c>
-      <c r="J35" s="52">
+      <c r="J35" s="51">
         <v>-0.41</v>
       </c>
-      <c r="K35" s="52">
+      <c r="K35" s="51">
         <v>-0.41</v>
       </c>
-      <c r="L35" s="52">
+      <c r="L35" s="51">
         <v>-0.41</v>
       </c>
-      <c r="M35" s="52">
+      <c r="M35" s="51">
         <v>-0.41</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B36" s="8"/>
-      <c r="D36" s="8"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
     </row>
     <row r="37" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B37" s="8"/>
-      <c r="D37" s="8"/>
+      <c r="B37" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="51">
+        <v>-0.35</v>
+      </c>
+      <c r="J37" s="51">
+        <v>-0.35</v>
+      </c>
+      <c r="K37" s="51">
+        <v>-0.35</v>
+      </c>
+      <c r="L37" s="51">
+        <v>-0.35</v>
+      </c>
+      <c r="M37" s="51">
+        <v>-0.35</v>
+      </c>
     </row>
     <row r="38" spans="2:13" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B38" s="8"/>
@@ -17958,7 +19380,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="C9:E9 C11:E11 C13:E13 C15:E15 I9:M9" formula="1"/>
+    <ignoredError sqref="C9:E9 C11:E11 C13:E13 C15:E15 I9:M9 I11:M11 I13:M13 I15:M15" formula="1"/>
     <ignoredError sqref="I8:M8" formulaRange="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
@@ -17967,7 +19389,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3438C9A7-B143-49B0-B772-F3CF41815D32}">
-  <dimension ref="B1:E18"/>
+  <dimension ref="B1:J26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6328125" style="22" customWidth="1"/>
@@ -17975,258 +19397,1020 @@
     <col min="3" max="3" width="11.36328125" style="22" customWidth="1"/>
     <col min="4" max="4" width="12.54296875" style="22" customWidth="1"/>
     <col min="5" max="5" width="11.36328125" style="22" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="22"/>
+    <col min="6" max="10" width="10.08984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B1" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="23"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F3" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="25">
+        <v>42004</v>
+      </c>
+      <c r="D4" s="25">
+        <v>42369</v>
+      </c>
+      <c r="E4" s="25">
+        <v>42735</v>
+      </c>
+      <c r="F4" s="25">
+        <v>43100</v>
+      </c>
+      <c r="G4" s="25">
+        <v>43465</v>
+      </c>
+      <c r="H4" s="25">
+        <v>43830</v>
+      </c>
+      <c r="I4" s="25">
+        <v>44196</v>
+      </c>
+      <c r="J4" s="25">
+        <v>44561</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B5,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>143.9</v>
+      </c>
+      <c r="D5" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B5,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>154.80000000000001</v>
+      </c>
+      <c r="E5" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B5,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>169.3</v>
+      </c>
+      <c r="F5" s="40">
+        <f ca="1">F19*'P&amp;L'!I6/360</f>
+        <v>163.67257936433663</v>
+      </c>
+      <c r="G5" s="40">
+        <f ca="1">G19*'P&amp;L'!J6/360</f>
+        <v>168.58275674526672</v>
+      </c>
+      <c r="H5" s="40">
+        <f ca="1">H19*'P&amp;L'!K6/360</f>
+        <v>173.64023944762474</v>
+      </c>
+      <c r="I5" s="40">
+        <f ca="1">I19*'P&amp;L'!L6/360</f>
+        <v>178.8494466310535</v>
+      </c>
+      <c r="J5" s="40">
+        <f ca="1">J19*'P&amp;L'!M6/360</f>
+        <v>184.21493002998508</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B6,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>84.999999999999986</v>
+      </c>
+      <c r="D6" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B6,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>92.000000000000014</v>
+      </c>
+      <c r="E6" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B6,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>110</v>
+      </c>
+      <c r="F6" s="40">
+        <f ca="1">-F21*'P&amp;L'!I$7/360</f>
+        <v>97.534303643238303</v>
+      </c>
+      <c r="G6" s="40">
+        <f ca="1">-G21*'P&amp;L'!J$7/360</f>
+        <v>100.46033275253548</v>
+      </c>
+      <c r="H6" s="40">
+        <f ca="1">-H21*'P&amp;L'!K$7/360</f>
+        <v>103.47414273511156</v>
+      </c>
+      <c r="I6" s="40">
+        <f ca="1">-I21*'P&amp;L'!L$7/360</f>
+        <v>106.57836701716488</v>
+      </c>
+      <c r="J6" s="40">
+        <f ca="1">-J21*'P&amp;L'!M$7/360</f>
+        <v>109.77571802767983</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B7,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>632.5</v>
+      </c>
+      <c r="D7" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B7,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>632.5</v>
+      </c>
+      <c r="E7" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B7,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>659.5</v>
+      </c>
+      <c r="F7" s="40">
+        <f>'Fixed Asset Roll Forward'!F8</f>
+        <v>673.57628458498027</v>
+      </c>
+      <c r="G7" s="40">
+        <f>'Fixed Asset Roll Forward'!G8</f>
+        <v>687.95301160774272</v>
+      </c>
+      <c r="H7" s="40">
+        <f>'Fixed Asset Roll Forward'!H8</f>
+        <v>702.6365936736787</v>
+      </c>
+      <c r="I7" s="40">
+        <f>'Fixed Asset Roll Forward'!I8</f>
+        <v>717.63358025801801</v>
+      </c>
+      <c r="J7" s="40">
+        <f>'Fixed Asset Roll Forward'!J8</f>
+        <v>732.95066062716148</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B8,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>24.8</v>
+      </c>
+      <c r="D8" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B8,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>21.8</v>
+      </c>
+      <c r="E8" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B8,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>220</v>
+      </c>
+      <c r="F8" s="40">
+        <f ca="1">E8+'Cash Flow'!F19</f>
+        <v>409.58712299964463</v>
+      </c>
+      <c r="G8" s="40">
+        <f ca="1">F8+'Cash Flow'!G19</f>
+        <v>559.82481259150927</v>
+      </c>
+      <c r="H8" s="40">
+        <f ca="1">G8+'Cash Flow'!H19</f>
+        <v>714.36121998729175</v>
+      </c>
+      <c r="I8" s="40">
+        <f ca="1">H8+'Cash Flow'!I19</f>
+        <v>873.18824782911304</v>
+      </c>
+      <c r="J8" s="40">
+        <f ca="1">I8+'Cash Flow'!J19</f>
+        <v>1036.2848142743742</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B9,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>45.9</v>
+      </c>
+      <c r="D9" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B9,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>46.9</v>
+      </c>
+      <c r="E9" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B9,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>68</v>
+      </c>
+      <c r="F9" s="40">
+        <f ca="1">F22*'P&amp;L'!I$6</f>
+        <v>56.146588971892989</v>
+      </c>
+      <c r="G9" s="40">
+        <f ca="1">G22*'P&amp;L'!J$6</f>
+        <v>57.830986641049783</v>
+      </c>
+      <c r="H9" s="40">
+        <f ca="1">H22*'P&amp;L'!K$6</f>
+        <v>59.565916240281283</v>
+      </c>
+      <c r="I9" s="40">
+        <f ca="1">I22*'P&amp;L'!L$6</f>
+        <v>61.352893727489722</v>
+      </c>
+      <c r="J9" s="40">
+        <f ca="1">J22*'P&amp;L'!M$6</f>
+        <v>63.193480539314415</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="41">
+        <f>SUM(C5:C9)</f>
+        <v>932.09999999999991</v>
+      </c>
+      <c r="D10" s="41">
+        <f>SUM(D5:D9)</f>
+        <v>947.99999999999989</v>
+      </c>
+      <c r="E10" s="41">
+        <f>SUM(E5:E9)</f>
+        <v>1226.8</v>
+      </c>
+      <c r="F10" s="41">
+        <f t="shared" ref="F10:J10" ca="1" si="0">SUM(F5:F9)</f>
+        <v>1400.5168795640927</v>
+      </c>
+      <c r="G10" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>1574.651900338104</v>
+      </c>
+      <c r="H10" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>1753.6781120839878</v>
+      </c>
+      <c r="I10" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>1937.6025354628393</v>
+      </c>
+      <c r="J10" s="41">
+        <f t="shared" ca="1" si="0"/>
+        <v>2126.4196034985148</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B12,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>68</v>
+      </c>
+      <c r="D12" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B12,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>68.900000000000006</v>
+      </c>
+      <c r="E12" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B12,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>68.900000000000006</v>
+      </c>
+      <c r="F12" s="40">
+        <f ca="1">-F20*'P&amp;L'!I$7/360</f>
+        <v>69.868814266268799</v>
+      </c>
+      <c r="G12" s="40">
+        <f ca="1">-G20*'P&amp;L'!J$7/360</f>
+        <v>71.964878694256868</v>
+      </c>
+      <c r="H12" s="40">
+        <f ca="1">-H20*'P&amp;L'!K$7/360</f>
+        <v>74.123825055084566</v>
+      </c>
+      <c r="I12" s="40">
+        <f ca="1">-I20*'P&amp;L'!L$7/360</f>
+        <v>76.347539806737103</v>
+      </c>
+      <c r="J12" s="40">
+        <f ca="1">-J20*'P&amp;L'!M$7/360</f>
+        <v>78.63796600093923</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B13,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>32.5</v>
+      </c>
+      <c r="D13" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B13,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="E13" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B13,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="F13" s="40">
+        <f>$E$13</f>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="G13" s="40">
+        <f t="shared" ref="G13:J13" si="1">$E$13</f>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="H13" s="40">
+        <f t="shared" si="1"/>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="I13" s="40">
+        <f t="shared" si="1"/>
+        <v>28.699999999999996</v>
+      </c>
+      <c r="J13" s="40">
+        <f t="shared" si="1"/>
+        <v>28.699999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B14,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>615.79999999999995</v>
+      </c>
+      <c r="D14" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B14,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>610.4</v>
+      </c>
+      <c r="E14" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B14,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>605</v>
+      </c>
+      <c r="F14" s="40">
+        <f>'Financial Liability'!F8</f>
+        <v>565.17884560503455</v>
+      </c>
+      <c r="G14" s="40">
+        <f>'Financial Liability'!G8</f>
+        <v>521.77378731452222</v>
+      </c>
+      <c r="H14" s="40">
+        <f>'Financial Liability'!H8</f>
+        <v>474.4622737778638</v>
+      </c>
+      <c r="I14" s="40">
+        <f>'Financial Liability'!I8</f>
+        <v>422.89272402290612</v>
+      </c>
+      <c r="J14" s="40">
+        <f>'Financial Liability'!J8</f>
+        <v>366.68191479000222</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B15,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>48.3</v>
+      </c>
+      <c r="D15" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B15,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>43.3</v>
+      </c>
+      <c r="E15" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B15,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>38.9</v>
+      </c>
+      <c r="F15" s="40">
+        <f ca="1">F23*'P&amp;L'!I$6</f>
+        <v>45.75366909990403</v>
+      </c>
+      <c r="G15" s="40">
+        <f ca="1">G23*'P&amp;L'!J$6</f>
+        <v>47.12627917290115</v>
+      </c>
+      <c r="H15" s="40">
+        <f ca="1">H23*'P&amp;L'!K$6</f>
+        <v>48.540067548088189</v>
+      </c>
+      <c r="I15" s="40">
+        <f ca="1">I23*'P&amp;L'!L$6</f>
+        <v>49.996269574530835</v>
+      </c>
+      <c r="J15" s="40">
+        <f ca="1">J23*'P&amp;L'!M$6</f>
+        <v>51.496157661766766</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="40">
+        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B16,'BS 2014'!$A:$A,0),MATCH(BS!C$4,'BS 2014'!$1:$1,0))</f>
+        <v>167.50000000000003</v>
+      </c>
+      <c r="D16" s="40">
+        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B16,'BS 2015'!$A:$A,0),MATCH(BS!D$4,'BS 2015'!$1:$1,0))</f>
+        <v>196.7</v>
+      </c>
+      <c r="E16" s="40">
+        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B16,'BS 2016'!$A:$A,0),MATCH(BS!E$4,'BS 2016'!$1:$1,0))</f>
+        <v>485.3</v>
+      </c>
+      <c r="F16" s="40">
+        <f ca="1">'Equity Schedule'!F9</f>
+        <v>691.01555059288535</v>
+      </c>
+      <c r="G16" s="40">
+        <f ca="1">'Equity Schedule'!G9</f>
+        <v>905.08695515642376</v>
+      </c>
+      <c r="H16" s="40">
+        <f ca="1">'Equity Schedule'!H9</f>
+        <v>1127.8519457029515</v>
+      </c>
+      <c r="I16" s="40">
+        <f ca="1">'Equity Schedule'!I9</f>
+        <v>1359.6660020586651</v>
+      </c>
+      <c r="J16" s="40">
+        <f ca="1">'Equity Schedule'!J9</f>
+        <v>1600.9035650458065</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="42">
+        <f>SUM(C12:C16)</f>
+        <v>932.09999999999991</v>
+      </c>
+      <c r="D17" s="42">
+        <f>SUM(D12:D16)</f>
+        <v>948</v>
+      </c>
+      <c r="E17" s="42">
+        <f>SUM(E12:E16)</f>
+        <v>1226.8</v>
+      </c>
+      <c r="F17" s="42">
+        <f t="shared" ref="F17:J17" ca="1" si="2">SUM(F12:F16)</f>
+        <v>1400.5168795640927</v>
+      </c>
+      <c r="G17" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>1574.651900338104</v>
+      </c>
+      <c r="H17" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>1753.678112083988</v>
+      </c>
+      <c r="I17" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>1937.6025354628391</v>
+      </c>
+      <c r="J17" s="42">
+        <f t="shared" ca="1" si="2"/>
+        <v>2126.4196034985148</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="58">
+        <f>C5/'P&amp;L'!C6*360</f>
+        <v>17.728952772073921</v>
+      </c>
+      <c r="D19" s="58">
+        <f>D5/'P&amp;L'!D6*360</f>
+        <v>18.675603217158177</v>
+      </c>
+      <c r="E19" s="58">
+        <f>E5/'P&amp;L'!E6*360</f>
+        <v>20.048684210526318</v>
+      </c>
+      <c r="F19" s="58">
+        <f>AVERAGE($C19:$E19)</f>
+        <v>18.817746733252804</v>
+      </c>
+      <c r="G19" s="58">
+        <f t="shared" ref="G19:J23" si="3">AVERAGE($C19:$E19)</f>
+        <v>18.817746733252804</v>
+      </c>
+      <c r="H19" s="58">
+        <f t="shared" si="3"/>
+        <v>18.817746733252804</v>
+      </c>
+      <c r="I19" s="58">
+        <f t="shared" si="3"/>
+        <v>18.817746733252804</v>
+      </c>
+      <c r="J19" s="58">
+        <f t="shared" si="3"/>
+        <v>18.817746733252804</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="59">
+        <f>-1*C12/'P&amp;L'!C$7*360</f>
+        <v>17.473233404710921</v>
+      </c>
+      <c r="D20" s="59">
+        <f>-1*D12/'P&amp;L'!D$7*360</f>
+        <v>17.934924078091107</v>
+      </c>
+      <c r="E20" s="59">
+        <f>-1*E12/'P&amp;L'!E$7*360</f>
+        <v>18.144842721287493</v>
+      </c>
+      <c r="F20" s="58">
+        <f t="shared" ref="F20:F23" si="4">AVERAGE($C20:$E20)</f>
+        <v>17.851000068029837</v>
+      </c>
+      <c r="G20" s="58">
+        <f t="shared" si="3"/>
+        <v>17.851000068029837</v>
+      </c>
+      <c r="H20" s="58">
+        <f t="shared" si="3"/>
+        <v>17.851000068029837</v>
+      </c>
+      <c r="I20" s="58">
+        <f t="shared" si="3"/>
+        <v>17.851000068029837</v>
+      </c>
+      <c r="J20" s="58">
+        <f t="shared" si="3"/>
+        <v>17.851000068029837</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="59">
+        <f>-1*C6/'P&amp;L'!C$7*360</f>
+        <v>21.841541755888645</v>
+      </c>
+      <c r="D21" s="59">
+        <f>-1*D6/'P&amp;L'!D$7*360</f>
+        <v>23.94793926247289</v>
+      </c>
+      <c r="E21" s="59">
+        <f>-1*E6/'P&amp;L'!E$7*360</f>
+        <v>28.96854425749817</v>
+      </c>
+      <c r="F21" s="58">
+        <f t="shared" si="4"/>
+        <v>24.919341758619904</v>
+      </c>
+      <c r="G21" s="58">
+        <f t="shared" si="3"/>
+        <v>24.919341758619904</v>
+      </c>
+      <c r="H21" s="58">
+        <f t="shared" si="3"/>
+        <v>24.919341758619904</v>
+      </c>
+      <c r="I21" s="58">
+        <f t="shared" si="3"/>
+        <v>24.919341758619904</v>
+      </c>
+      <c r="J21" s="58">
+        <f t="shared" si="3"/>
+        <v>24.919341758619904</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="60">
+        <f>C9/'P&amp;L'!C$6</f>
+        <v>1.5708418891170431E-2</v>
+      </c>
+      <c r="D22" s="60">
+        <f>D9/'P&amp;L'!D$6</f>
+        <v>1.5717158176943698E-2</v>
+      </c>
+      <c r="E22" s="60">
+        <f>E9/'P&amp;L'!E$6</f>
+        <v>2.2368421052631579E-2</v>
+      </c>
+      <c r="F22" s="60">
+        <f t="shared" si="4"/>
+        <v>1.7931332706915236E-2</v>
+      </c>
+      <c r="G22" s="60">
+        <f t="shared" si="3"/>
+        <v>1.7931332706915236E-2</v>
+      </c>
+      <c r="H22" s="60">
+        <f t="shared" si="3"/>
+        <v>1.7931332706915236E-2</v>
+      </c>
+      <c r="I22" s="60">
+        <f t="shared" si="3"/>
+        <v>1.7931332706915236E-2</v>
+      </c>
+      <c r="J22" s="60">
+        <f t="shared" si="3"/>
+        <v>1.7931332706915236E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="60">
+        <f>C15/'P&amp;L'!C$6</f>
+        <v>1.6529774127310062E-2</v>
+      </c>
+      <c r="D23" s="60">
+        <f>D15/'P&amp;L'!D$6</f>
+        <v>1.4510723860589811E-2</v>
+      </c>
+      <c r="E23" s="60">
+        <f>E15/'P&amp;L'!E$6</f>
+        <v>1.2796052631578948E-2</v>
+      </c>
+      <c r="F23" s="60">
+        <f t="shared" si="4"/>
+        <v>1.4612183539826273E-2</v>
+      </c>
+      <c r="G23" s="60">
+        <f t="shared" si="3"/>
+        <v>1.4612183539826273E-2</v>
+      </c>
+      <c r="H23" s="60">
+        <f t="shared" si="3"/>
+        <v>1.4612183539826273E-2</v>
+      </c>
+      <c r="I23" s="60">
+        <f t="shared" si="3"/>
+        <v>1.4612183539826273E-2</v>
+      </c>
+      <c r="J23" s="60">
+        <f t="shared" si="3"/>
+        <v>1.4612183539826273E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="38" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="25">
-        <v>42004</v>
-      </c>
-      <c r="D3" s="25">
-        <v>42369</v>
-      </c>
-      <c r="E3" s="25">
-        <v>42735</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B4,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>143.9</v>
-      </c>
-      <c r="D4" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B4,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>154.80000000000001</v>
-      </c>
-      <c r="E4" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B4,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>169.3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B5,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>84.999999999999986</v>
-      </c>
-      <c r="D5" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B5,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>92.000000000000014</v>
-      </c>
-      <c r="E5" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B5,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B6,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>632.5</v>
-      </c>
-      <c r="D6" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B6,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>632.5</v>
-      </c>
-      <c r="E6" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B6,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>659.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B7,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>24.8</v>
-      </c>
-      <c r="D7" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B7,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>21.8</v>
-      </c>
-      <c r="E7" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B7,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B8,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>45.9</v>
-      </c>
-      <c r="D8" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B8,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>46.9</v>
-      </c>
-      <c r="E8" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B8,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="41">
-        <f>SUM(C4:C8)</f>
-        <v>932.09999999999991</v>
-      </c>
-      <c r="D9" s="41">
-        <f>SUM(D4:D8)</f>
-        <v>947.99999999999989</v>
-      </c>
-      <c r="E9" s="41">
-        <f>SUM(E4:E8)</f>
-        <v>1226.8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B11,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>68</v>
-      </c>
-      <c r="D11" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B11,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>68.900000000000006</v>
-      </c>
-      <c r="E11" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B11,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>68.900000000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B12,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>32.5</v>
-      </c>
-      <c r="D12" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B12,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>28.699999999999996</v>
-      </c>
-      <c r="E12" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B12,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>28.699999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B13,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>615.79999999999995</v>
-      </c>
-      <c r="D13" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B13,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>610.4</v>
-      </c>
-      <c r="E13" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B13,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>605</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B14,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>48.3</v>
-      </c>
-      <c r="D14" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B14,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>43.3</v>
-      </c>
-      <c r="E14" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B14,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>38.9</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="40">
-        <f>INDEX('BS 2014'!$1:$1048576,MATCH(BS!$B15,'BS 2014'!$A:$A,0),MATCH(BS!C$3,'BS 2014'!$1:$1,0))</f>
-        <v>167.50000000000003</v>
-      </c>
-      <c r="D15" s="40">
-        <f>INDEX('BS 2015'!$1:$1048576,MATCH(BS!$B15,'BS 2015'!$A:$A,0),MATCH(BS!D$3,'BS 2015'!$1:$1,0))</f>
-        <v>196.7</v>
-      </c>
-      <c r="E15" s="40">
-        <f>INDEX('BS 2016'!$1:$1048576,MATCH(BS!$B15,'BS 2016'!$A:$A,0),MATCH(BS!E$3,'BS 2016'!$1:$1,0))</f>
-        <v>485.3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="42">
-        <f>SUM(C11:C15)</f>
-        <v>932.09999999999991</v>
-      </c>
-      <c r="D16" s="42">
-        <f>SUM(D11:D15)</f>
-        <v>948</v>
-      </c>
-      <c r="E16" s="42">
-        <f>SUM(E11:E15)</f>
-        <v>1226.8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="39">
-        <f>C9-C16</f>
+      <c r="C26" s="39">
+        <f>C10-C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="39">
-        <f t="shared" ref="D18:E18" si="0">D9-D16</f>
+      <c r="D26" s="39">
+        <f>D10-D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="39">
-        <f t="shared" si="0"/>
+      <c r="E26" s="39">
+        <f>E10-E17</f>
         <v>0</v>
       </c>
+      <c r="F26" s="39">
+        <f t="shared" ref="F26:J26" ca="1" si="5">F10-F17</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="39">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="39">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="39">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="39">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:J3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C9" formulaRange="1"/>
+    <ignoredError sqref="C10 F10:J10" formulaRange="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FB3C7F-E809-4B4B-9D19-048685C4D0E4}">
+  <dimension ref="B1:J11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.6328125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="10.08984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F3" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="25">
+        <v>42004</v>
+      </c>
+      <c r="D4" s="25">
+        <v>42369</v>
+      </c>
+      <c r="E4" s="25">
+        <v>42735</v>
+      </c>
+      <c r="F4" s="25">
+        <v>43100</v>
+      </c>
+      <c r="G4" s="25">
+        <v>43465</v>
+      </c>
+      <c r="H4" s="25">
+        <v>43830</v>
+      </c>
+      <c r="I4" s="25">
+        <v>44196</v>
+      </c>
+      <c r="J4" s="25">
+        <v>44561</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="64">
+        <f>BS!C7</f>
+        <v>632.5</v>
+      </c>
+      <c r="E5" s="64">
+        <f>BS!D7</f>
+        <v>632.5</v>
+      </c>
+      <c r="F5" s="64">
+        <f>E8</f>
+        <v>659.5</v>
+      </c>
+      <c r="G5" s="64">
+        <f t="shared" ref="G5:J5" si="0">F8</f>
+        <v>673.57628458498027</v>
+      </c>
+      <c r="H5" s="64">
+        <f t="shared" si="0"/>
+        <v>687.95301160774272</v>
+      </c>
+      <c r="I5" s="64">
+        <f>H8</f>
+        <v>702.6365936736787</v>
+      </c>
+      <c r="J5" s="64">
+        <f>I8</f>
+        <v>717.63358025801801</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="64">
+        <f>'P&amp;L'!D11</f>
+        <v>-44</v>
+      </c>
+      <c r="E6" s="64">
+        <f>'P&amp;L'!E11</f>
+        <v>-41</v>
+      </c>
+      <c r="F6" s="64">
+        <f>F$5*F10</f>
+        <v>-44.314229249011859</v>
+      </c>
+      <c r="G6" s="64">
+        <f t="shared" ref="G6:J7" si="1">G$5*G10</f>
+        <v>-45.260066553140966</v>
+      </c>
+      <c r="H6" s="64">
+        <f t="shared" si="1"/>
+        <v>-46.22609168905781</v>
+      </c>
+      <c r="I6" s="64">
+        <f t="shared" si="1"/>
+        <v>-47.212735543290663</v>
+      </c>
+      <c r="J6" s="64">
+        <f t="shared" si="1"/>
+        <v>-48.22043819915536</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="64">
+        <f>D8-D5-D6</f>
+        <v>44</v>
+      </c>
+      <c r="E7" s="64">
+        <f>E8-E5-E6</f>
+        <v>68</v>
+      </c>
+      <c r="F7" s="64">
+        <f>F$5*F11</f>
+        <v>58.390513833992095</v>
+      </c>
+      <c r="G7" s="64">
+        <f t="shared" si="1"/>
+        <v>59.63679357590339</v>
+      </c>
+      <c r="H7" s="64">
+        <f t="shared" si="1"/>
+        <v>60.909673754993825</v>
+      </c>
+      <c r="I7" s="64">
+        <f t="shared" si="1"/>
+        <v>62.209722127630052</v>
+      </c>
+      <c r="J7" s="64">
+        <f t="shared" si="1"/>
+        <v>63.537518568298829</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26">
+        <f>BS!D7</f>
+        <v>632.5</v>
+      </c>
+      <c r="E8" s="26">
+        <f>BS!E7</f>
+        <v>659.5</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" ref="D8:J8" si="2">SUM(F5:F7)</f>
+        <v>673.57628458498027</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" si="2"/>
+        <v>687.95301160774272</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="2"/>
+        <v>702.6365936736787</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="2"/>
+        <v>717.63358025801801</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="2"/>
+        <v>732.95066062716148</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60">
+        <f>D6/D5</f>
+        <v>-6.9565217391304349E-2</v>
+      </c>
+      <c r="E10" s="60">
+        <f>E6/E5</f>
+        <v>-6.4822134387351779E-2</v>
+      </c>
+      <c r="F10" s="60">
+        <f>AVERAGE($D10:$E10)</f>
+        <v>-6.7193675889328064E-2</v>
+      </c>
+      <c r="G10" s="60">
+        <f t="shared" ref="G10:J11" si="3">AVERAGE($D10:$E10)</f>
+        <v>-6.7193675889328064E-2</v>
+      </c>
+      <c r="H10" s="60">
+        <f t="shared" si="3"/>
+        <v>-6.7193675889328064E-2</v>
+      </c>
+      <c r="I10" s="60">
+        <f t="shared" si="3"/>
+        <v>-6.7193675889328064E-2</v>
+      </c>
+      <c r="J10" s="60">
+        <f t="shared" si="3"/>
+        <v>-6.7193675889328064E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60">
+        <f>D7/D5</f>
+        <v>6.9565217391304349E-2</v>
+      </c>
+      <c r="E11" s="60">
+        <f>E7/E5</f>
+        <v>0.10750988142292491</v>
+      </c>
+      <c r="F11" s="60">
+        <f>AVERAGE($D11:$E11)</f>
+        <v>8.8537549407114627E-2</v>
+      </c>
+      <c r="G11" s="60">
+        <f t="shared" si="3"/>
+        <v>8.8537549407114627E-2</v>
+      </c>
+      <c r="H11" s="60">
+        <f t="shared" si="3"/>
+        <v>8.8537549407114627E-2</v>
+      </c>
+      <c r="I11" s="60">
+        <f t="shared" si="3"/>
+        <v>8.8537549407114627E-2</v>
+      </c>
+      <c r="J11" s="60">
+        <f t="shared" si="3"/>
+        <v>8.8537549407114627E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="F8:J8" formulaRange="1"/>
+    <ignoredError sqref="D8" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>